--- a/docs/basics/table1.xlsx
+++ b/docs/basics/table1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\plume\Documents\GitHub\Note\docs\basics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDC9C449-1D79-4699-BE23-EF6A57CCD378}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD73B8E-0A33-43F1-AFD5-2D48FD254E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="855" yWindow="3885" windowWidth="17520" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,11 +35,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>A</t>
+    <t>代碼 A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>B</t>
+    <t>代碼 B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -48,7 +48,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -88,7 +88,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
